--- a/LRU_TestCases.xlsx
+++ b/LRU_TestCases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tranphuongmai/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tranphuongmai/Downloads/LRU - BTL 21:06/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7373CDE-93F1-544E-ABCF-00AEE79A4477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF859EB-4A92-6C4E-8D15-672A37CE10BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,46 +117,6 @@
 frames = 3</t>
   </si>
   <si>
-    <t>Total Page Faults = 8
-Page Fault Rate = 80.00%
-Trace:
-Reference 7:  -&gt; Page Fault: YES (MISS - Added to free frame)
-    Memory state: [7]
-Reference 0: -&gt; Page Fault: YES (MISS - Added to free frame)
-    Memory state: [7, 0]
-Reference 1:  -&gt; Page Fault: YES (MISS - Added to free frame)
-    Memory state: [7, 0, 1]
-Reference 2:  -&gt; Page Fault: YES (MISS - Replaced page 7)
-    Memory state: [0, 1, 2]
-Reference 0:  -&gt; Page Fault: NO  (HIT)
-    Memory state: [1, 2, 0]
-Reference 3:  -&gt; Page Fault: YES (MISS - Replaced page 1)
-    Memory state: [2, 0, 3]
-Reference 0:  -&gt; Page Fault: NO  (HIT)
-    Memory state: [2, 3, 0]
-Reference 4:  -&gt; Page Fault: YES (MISS - Replaced page 2)
-    Memory state: [3, 0, 4]
-Reference 2:  -&gt; Page Fault: YES (MISS - Replaced page 3)
-    Memory state: [0, 4, 2]
-Reference 3:  -&gt; Page Fault: YES (MISS - Replaced page 0)
-    Memory state: [4, 2, 3]</t>
-  </si>
-  <si>
-    <t>Total Page Faults = 5
-Page Fault Rate = 100.00%
-Trace: 
-Reference 1:  -&gt; Page Fault: YES (MISS - Added to free frame)
-    Memory state: [1]
-Reference 2:  -&gt; Page Fault: YES (MISS - Added to free frame)
-    Memory state: [1, 2]
-Reference 3:  -&gt; Page Fault: YES (MISS - Added to free frame)
-    Memory state: [1, 2, 3]
-Reference 4:  -&gt; Page Fault: YES (MISS - Replaced page 1)
-    Memory state: [2, 3, 4]
-Reference 5:  -&gt; Page Fault: YES (MISS - Replaced page 2)
-    Memory state: [3, 4, 5]</t>
-  </si>
-  <si>
     <t>Total Page Faults = 1
 Page Fault Rate = 20.00%
 Trace:
@@ -176,6 +136,68 @@
     Memory state: [1]</t>
   </si>
   <si>
+    <t>Total Page Faults: 5
+Page Fault Rate  : 100.00%
+Trace:
+Reference 1: -&gt; Page Fault: YES (MISS - Added to free frame)
+    Memory state: [1]
+Reference 2: -&gt; Page Fault: YES (MISS - Replaced page 1)
+    Memory state: [2]
+Reference 1: -&gt; Page Fault: YES (MISS - Replaced page 2)
+    Memory state: [1]
+Reference 2: -&gt; Page Fault: YES (MISS - Replaced page 1)
+    Memory state: [2]
+Reference 1: -&gt; Page Fault: YES (MISS - Replaced page 2)
+    Memory state: [1]</t>
+  </si>
+  <si>
+    <t>Total Page Faults = 1
+Page Fault Rate = 100.00%
+Trace:
+Reference 5: -&gt; Page Fault: YES (MISS - Added to free frame)
+    Memory state: [5]</t>
+  </si>
+  <si>
+    <t>Total Page Faults = 8
+Page Fault Rate = 80.00%
+Trace:
+Reference 7: -&gt; Page Fault: YES (MISS - Added to free frame)
+    Memory state: [7]
+Reference 0: -&gt; Page Fault: YES (MISS - Added to free frame)
+    Memory state: [7, 0]
+Reference 1: -&gt; Page Fault: YES (MISS - Added to free frame)
+    Memory state: [7, 0, 1]
+Reference 2: -&gt; Page Fault: YES (MISS - Replaced page 7)
+    Memory state: [2, 0, 1]
+Reference 0: -&gt; Page Fault: NO  (HIT)
+    Memory state: [2, 0, 1]
+Reference 3: -&gt; Page Fault: YES (MISS - Replaced page 1)
+    Memory state: [2, 0, 3]
+Reference 0: -&gt; Page Fault: NO  (HIT)
+    Memory state: [2, 0, 3]
+Reference 4: -&gt; Page Fault: YES (MISS - Replaced page 2)
+    Memory state: [4, 0, 3]
+Reference 2: -&gt; Page Fault: YES (MISS - Replaced page 3)
+    Memory state: [4, 0, 2]
+Reference 3: -&gt; Page Fault: YES (MISS - Replaced page 0)
+    Memory state: [4, 3, 2]</t>
+  </si>
+  <si>
+    <t>Total Page Faults = 5
+Page Fault Rate = 100.00%
+Trace: 
+Reference 1: -&gt; Page Fault: YES (MISS - Added to free frame)
+    Memory state: [1]
+Reference 2: -&gt; Page Fault: YES (MISS - Added to free frame)
+    Memory state: [1, 2]
+Reference 3: -&gt; Page Fault: YES (MISS - Added to free frame)
+    Memory state: [1, 2, 3]
+Reference 4: -&gt; Page Fault: YES (MISS - Replaced page 1)
+    Memory state: [4, 2, 3]
+Reference 5: -&gt; Page Fault: YES (MISS - Replaced page 2)
+    Memory state: [4, 5, 3]</t>
+  </si>
+  <si>
     <t>Total Page Faults: 4
 Page Fault Rate  : 50.00%
 Trace:
@@ -188,35 +210,13 @@
 Reference 4: -&gt; Page Fault: YES (MISS - Added to free frame)
     Memory state: [1, 2, 3, 4]
 Reference 1: -&gt; Page Fault: NO  (HIT)
-    Memory state: [2, 3, 4, 1]
+    Memory state: [1, 2, 3, 4]
 Reference 2: -&gt; Page Fault: NO  (HIT)
-    Memory state: [3, 4, 1, 2]
+    Memory state: [1, 2, 3, 4]
 Reference 3: -&gt; Page Fault: NO  (HIT)
-    Memory state: [4, 1, 2, 3]
+    Memory state: [1, 2, 3, 4]
 Reference 4: -&gt; Page Fault: NO  (HIT)
     Memory state: [1, 2, 3, 4]</t>
-  </si>
-  <si>
-    <t>Total Page Faults: 5
-Page Fault Rate  : 100.00%
-Trace:
-Reference 1: -&gt; Page Fault: YES (MISS - Added to free frame)
-    Memory state: [1]
-Reference 2: -&gt; Page Fault: YES (MISS - Replaced page 1)
-    Memory state: [2]
-Reference 1: -&gt; Page Fault: YES (MISS - Replaced page 2)
-    Memory state: [1]
-Reference 2: -&gt; Page Fault: YES (MISS - Replaced page 1)
-    Memory state: [2]
-Reference 1: -&gt; Page Fault: YES (MISS - Replaced page 2)
-    Memory state: [1]</t>
-  </si>
-  <si>
-    <t>Total Page Faults = 1
-Page Fault Rate = 100.00%
-Trace:
-Reference 5: -&gt; Page Fault: YES (MISS - Added to free frame)
-    Memory state: [5]</t>
   </si>
 </sst>
 </file>
@@ -285,7 +285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -293,10 +293,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -493,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -502,7 +501,7 @@
     <col min="4" max="4" width="77.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -516,7 +515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="350" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="350" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -527,16 +526,12 @@
         <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+        <v>25</v>
+      </c>
       <c r="G2" s="3"/>
-      <c r="H2" s="4"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="4"/>
-    </row>
-    <row r="3" spans="1:10" ht="193" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:9" ht="193" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -547,16 +542,13 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="4"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-    </row>
-    <row r="4" spans="1:10" ht="271" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:9" ht="271" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -567,10 +559,10 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="279" customHeight="1" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="279" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
@@ -581,11 +573,11 @@
         <v>15</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:10" ht="200" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="200" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -596,10 +588,10 @@
         <v>18</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
@@ -610,56 +602,32 @@
         <v>21</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:10" ht="213" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:9" ht="213" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:9" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:9" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
